--- a/output/palmer_drought_trendlines/state/Year.xlsx
+++ b/output/palmer_drought_trendlines/state/Year.xlsx
@@ -43,13 +43,16 @@
     <t>Trend Y</t>
   </si>
   <si>
+    <t>Arizona</t>
+  </si>
+  <si>
     <t>New Mexico</t>
   </si>
   <si>
     <t>Utah</t>
   </si>
   <si>
-    <t>Arizona</t>
+    <t>California</t>
   </si>
   <si>
     <t>Wyoming</t>
@@ -58,93 +61,90 @@
     <t>Nevada</t>
   </si>
   <si>
+    <t>Colorado</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
     <t>Florida</t>
   </si>
   <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
     <t>Oregon</t>
   </si>
   <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
     <t>Idaho</t>
   </si>
   <si>
-    <t>Delaware</t>
-  </si>
-  <si>
     <t>New Jersey</t>
   </si>
   <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
     <t>Connecticut</t>
   </si>
   <si>
-    <t>Washington</t>
-  </si>
-  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>South Carolina</t>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
   <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>North Dakota</t>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
   </si>
   <si>
     <t>Kansas</t>
   </si>
   <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
   </si>
   <si>
     <t>Missouri</t>
   </si>
   <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
     <t>Louisiana</t>
   </si>
   <si>
-    <t>Minnesota</t>
-  </si>
-  <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>South Dakota</t>
-  </si>
-  <si>
     <t>Alabama</t>
   </si>
   <si>
@@ -157,31 +157,31 @@
     <t>Mississippi</t>
   </si>
   <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
     <t>Illinois</t>
   </si>
   <si>
-    <t>Wisconsin</t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Tennessee</t>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
   </si>
   <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
     <t>Indiana</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
   </si>
   <si>
     <t>Vermont</t>
@@ -576,234 +576,234 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.01988900078092525</v>
+        <v>-0.0350917282797556</v>
       </c>
       <c r="D2">
-        <v>1.147173995595048</v>
+        <v>1.714998101313891</v>
       </c>
       <c r="E2">
-        <v>-0.2977813541553877</v>
+        <v>-0.3092330069513365</v>
       </c>
       <c r="F2">
-        <v>0.0005248940378375429</v>
+        <v>0.0003087215118444015</v>
       </c>
       <c r="G2">
-        <v>0.005592174717482334</v>
+        <v>0.009465019212448085</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-1.458285106706159</v>
+        <v>-2.882018303334093</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.0190456918915709</v>
+        <v>-0.03441514960197162</v>
       </c>
       <c r="D3">
-        <v>1.191465582245657</v>
+        <v>1.955555935292778</v>
       </c>
       <c r="E3">
-        <v>-0.2816700564560702</v>
+        <v>-0.294177350759346</v>
       </c>
       <c r="F3">
-        <v>0.001068385595816397</v>
+        <v>0.0006175706680827408</v>
       </c>
       <c r="G3">
-        <v>0.005690291325962438</v>
+        <v>0.009806486746986792</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-1.303520055550131</v>
+        <v>-2.552828662565505</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.01869606106075141</v>
+        <v>-0.03315620766002445</v>
       </c>
       <c r="D4">
-        <v>0.8674293010665189</v>
+        <v>1.823903318903319</v>
       </c>
       <c r="E4">
-        <v>-0.3034111258934013</v>
+        <v>-0.2733430080875031</v>
       </c>
       <c r="F4">
-        <v>0.0004054387625779929</v>
+        <v>0.001517991739923782</v>
       </c>
       <c r="G4">
-        <v>0.005149628720839836</v>
+        <v>0.01023346333108652</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-1.581754697891916</v>
+        <v>-2.519559884559885</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.01801088673900474</v>
+        <v>-0.03207462619073708</v>
       </c>
       <c r="D5">
-        <v>1.233706587898317</v>
+        <v>1.576973874079138</v>
       </c>
       <c r="E5">
-        <v>-0.2390919206180785</v>
+        <v>-0.304808404870169</v>
       </c>
       <c r="F5">
-        <v>0.005762598943629195</v>
+        <v>0.0003799627420766842</v>
       </c>
       <c r="G5">
-        <v>0.006415291262344212</v>
+        <v>0.008789994807055682</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-1.125719574911304</v>
+        <v>-2.62480215690742</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.01716776637240966</v>
+        <v>-0.0320594077142892</v>
       </c>
       <c r="D6">
-        <v>0.7561409340450695</v>
+        <v>1.804714437609175</v>
       </c>
       <c r="E6">
-        <v>-0.2671989318799165</v>
+        <v>-0.2563516008142526</v>
       </c>
       <c r="F6">
-        <v>0.001953590493780401</v>
+        <v>0.003007328332491556</v>
       </c>
       <c r="G6">
-        <v>0.005430287790349646</v>
+        <v>0.01060198553012712</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-1.492836460740596</v>
+        <v>-2.39506797296271</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.01689046088503702</v>
+        <v>-0.03136115792604342</v>
       </c>
       <c r="D7">
-        <v>1.317436299081036</v>
+        <v>1.388903318903318</v>
       </c>
       <c r="E7">
-        <v>-0.273762187499992</v>
+        <v>-0.259986870084001</v>
       </c>
       <c r="F7">
-        <v>0.001491771994937527</v>
+        <v>0.002607673479933152</v>
       </c>
       <c r="G7">
-        <v>0.005204511427343878</v>
+        <v>0.01021578443127013</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-0.8952140768588133</v>
+        <v>-2.719408369408369</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.01570474404013404</v>
+        <v>-0.02800987548677384</v>
       </c>
       <c r="D8">
-        <v>0.71649262496067</v>
+        <v>1.543232702969545</v>
       </c>
       <c r="E8">
-        <v>-0.2960997379022215</v>
+        <v>-0.2365335952691653</v>
       </c>
       <c r="F8">
-        <v>0.0005664142431574855</v>
+        <v>0.006322359021224115</v>
       </c>
       <c r="G8">
-        <v>0.004443200776316301</v>
+        <v>0.01009124138617706</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-1.340828844296889</v>
+        <v>-2.126060985797828</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.0153934445139318</v>
+        <v>-0.02692457201296092</v>
       </c>
       <c r="D9">
-        <v>1.018430247697165</v>
+        <v>1.762978658768132</v>
       </c>
       <c r="E9">
-        <v>-0.2309009477201977</v>
+        <v>-0.2505077275860475</v>
       </c>
       <c r="F9">
-        <v>0.007728331174476731</v>
+        <v>0.003766514290194253</v>
       </c>
       <c r="G9">
-        <v>0.005689067807622939</v>
+        <v>0.009126048545820295</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-0.9981109836279012</v>
+        <v>-1.764140274929749</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,83 +814,83 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.01127596737953737</v>
+        <v>-0.02254352919077708</v>
       </c>
       <c r="D10">
-        <v>0.5485289658128003</v>
+        <v>1.098747626642363</v>
       </c>
       <c r="E10">
-        <v>-0.2638335434060595</v>
+        <v>-0.2254473416057909</v>
       </c>
       <c r="F10">
-        <v>0.002237609988798468</v>
+        <v>0.009346649241382555</v>
       </c>
       <c r="G10">
-        <v>0.00361563911243983</v>
+        <v>0.00854432801571225</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-0.9286227609065953</v>
+        <v>-1.854454697349434</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.007822376402988235</v>
+        <v>-0.02048946968392529</v>
       </c>
       <c r="D11">
-        <v>0.2450568520869272</v>
+        <v>1.035822890559733</v>
       </c>
       <c r="E11">
-        <v>-0.1835118613338989</v>
+        <v>-0.2149599378873998</v>
       </c>
       <c r="F11">
-        <v>0.03518185189089076</v>
+        <v>0.01331544747771309</v>
       </c>
       <c r="G11">
-        <v>0.003675057520554858</v>
+        <v>0.008164477618906351</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-0.7796744567045317</v>
+        <v>-1.64829763803448</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.007309923092652819</v>
+        <v>-0.01781811398725822</v>
       </c>
       <c r="D12">
-        <v>0.2409175671863643</v>
+        <v>0.6535258601048074</v>
       </c>
       <c r="E12">
-        <v>-0.1511068067091744</v>
+        <v>-0.1836691149431781</v>
       </c>
       <c r="F12">
-        <v>0.08371638326870454</v>
+        <v>0.03502274579688019</v>
       </c>
       <c r="G12">
-        <v>0.004194125681241665</v>
+        <v>0.008363772195419665</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-0.716682357951155</v>
+        <v>-1.680647072226019</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,286 +901,286 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.004175611714425352</v>
+        <v>-0.01742805139149052</v>
       </c>
       <c r="D13">
-        <v>0.04224445041174368</v>
+        <v>0.7155525176577808</v>
       </c>
       <c r="E13">
-        <v>-0.1043390303045783</v>
+        <v>-0.1825687841851854</v>
       </c>
       <c r="F13">
-        <v>0.2338046395972743</v>
+        <v>0.03614888596134367</v>
       </c>
       <c r="G13">
-        <v>0.003490797613579491</v>
+        <v>0.008231698343545112</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-0.5047606841779775</v>
+        <v>-1.567522214627478</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.00374677244066844</v>
+        <v>-0.01710592407458619</v>
       </c>
       <c r="D14">
-        <v>0.225455983031171</v>
+        <v>0.7026855016328704</v>
       </c>
       <c r="E14">
-        <v>-0.1023619095298329</v>
+        <v>-0.1804365190283077</v>
       </c>
       <c r="F14">
-        <v>0.2428334487114029</v>
+        <v>0.03841812465724645</v>
       </c>
       <c r="G14">
-        <v>0.003193449096181511</v>
+        <v>0.008178300072744185</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-0.2653712066963946</v>
+        <v>-1.538190552137921</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.003584701878121494</v>
+        <v>-0.01678692741569399</v>
       </c>
       <c r="D15">
-        <v>0.1305185718625567</v>
+        <v>0.5974982911825019</v>
       </c>
       <c r="E15">
-        <v>-0.09794494326419334</v>
+        <v>-0.168565848745834</v>
       </c>
       <c r="F15">
-        <v>0.2638714047717573</v>
+        <v>0.05334676505950871</v>
       </c>
       <c r="G15">
-        <v>0.003194523978629701</v>
+        <v>0.008609352094543396</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.339077374171359</v>
+        <v>-1.601589200273411</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.00321669613460637</v>
+        <v>-0.01654527540224607</v>
       </c>
       <c r="D16">
-        <v>0.03958158382970425</v>
+        <v>0.8440943267259058</v>
       </c>
       <c r="E16">
-        <v>-0.08373795299694695</v>
+        <v>-0.1770043513174329</v>
       </c>
       <c r="F16">
-        <v>0.3397783922012347</v>
+        <v>0.04232159730840781</v>
       </c>
       <c r="G16">
-        <v>0.003357283462019846</v>
+        <v>0.0080687486196152</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-0.3818056098037302</v>
+        <v>-1.32333675096833</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.003181212859152939</v>
+        <v>-0.01511925198144563</v>
       </c>
       <c r="D17">
-        <v>-0.08823860245852719</v>
+        <v>0.6018261562998406</v>
       </c>
       <c r="E17">
-        <v>-0.04824129418075636</v>
+        <v>-0.1587048136349985</v>
       </c>
       <c r="F17">
-        <v>0.5828005099063995</v>
+        <v>0.06912921019146151</v>
       </c>
       <c r="G17">
-        <v>0.005776917481547938</v>
+        <v>0.008249528688465213</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-0.5049774870075622</v>
+        <v>-1.378795853269537</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.002973476618084322</v>
+        <v>-0.01495773611683615</v>
       </c>
       <c r="D18">
-        <v>0.08096762468942928</v>
+        <v>0.5794539378749903</v>
       </c>
       <c r="E18">
-        <v>-0.07853227949855755</v>
+        <v>-0.1609673931508142</v>
       </c>
       <c r="F18">
-        <v>0.3707502507116912</v>
+        <v>0.06520827822414346</v>
       </c>
       <c r="G18">
-        <v>0.003310558640421835</v>
+        <v>0.008043697151658057</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-0.3085578122796169</v>
+        <v>-1.380009493430546</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.002881307623674036</v>
+        <v>-0.01477625361112705</v>
       </c>
       <c r="D19">
-        <v>0.006408730158730114</v>
+        <v>0.5191577428419532</v>
       </c>
       <c r="E19">
-        <v>-0.07357385786238758</v>
+        <v>-0.1528105056046239</v>
       </c>
       <c r="F19">
-        <v>0.4018080486586681</v>
+        <v>0.08024794653065741</v>
       </c>
       <c r="G19">
-        <v>0.003425435449024863</v>
+        <v>0.008381247994061201</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-0.3710425685425686</v>
+        <v>-1.416531480215691</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.002571603552849607</v>
+        <v>-0.01426857393309784</v>
       </c>
       <c r="D20">
-        <v>0.02854194468856122</v>
+        <v>0.5758794714057871</v>
       </c>
       <c r="E20">
-        <v>-0.05703342190169268</v>
+        <v>-0.1564651429664039</v>
       </c>
       <c r="F20">
-        <v>0.5159759604028946</v>
+        <v>0.07319684609158181</v>
       </c>
       <c r="G20">
-        <v>0.003948166156400016</v>
+        <v>0.007899672424783066</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-0.3083381207347373</v>
+        <v>-1.293303713830029</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.002272778829198505</v>
+        <v>-0.01389920846529927</v>
       </c>
       <c r="D21">
-        <v>-0.007844747149258369</v>
+        <v>0.3708779524568999</v>
       </c>
       <c r="E21">
-        <v>-0.05512180616219899</v>
+        <v>-0.1169134233669247</v>
       </c>
       <c r="F21">
-        <v>0.5301641800236319</v>
+        <v>0.1818631029711424</v>
       </c>
       <c r="G21">
-        <v>0.003610782027476563</v>
+        <v>0.01035536501832537</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-0.3055787737742626</v>
+        <v>-1.449918356497304</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-5.604716410834859E-05</v>
+        <v>-0.01293594847632614</v>
       </c>
       <c r="D22">
-        <v>0.6043429867959943</v>
+        <v>0.655435938330675</v>
       </c>
       <c r="E22">
-        <v>-0.0007808961002107592</v>
+        <v>-0.1377497579237138</v>
       </c>
       <c r="F22">
-        <v>0.9929097072279159</v>
+        <v>0.1152356958748268</v>
       </c>
       <c r="G22">
-        <v>0.006294896304329669</v>
+        <v>0.008157851491909651</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>0.5970008082978007</v>
+        <v>-1.039173312068049</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,83 +1191,83 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>0.0008781613744880676</v>
+        <v>-0.01193869475910457</v>
       </c>
       <c r="D23">
-        <v>0.6492246579652595</v>
+        <v>1.286327941064783</v>
       </c>
       <c r="E23">
-        <v>0.01434474465383192</v>
+        <v>-0.1062923615365886</v>
       </c>
       <c r="F23">
-        <v>0.8703220460911437</v>
+        <v>0.2251180339239412</v>
       </c>
       <c r="G23">
-        <v>0.005368650664222893</v>
+        <v>0.00979525639216423</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>0.7642637980231963</v>
+        <v>-0.277641072377915</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>0.001984781896249496</v>
+        <v>-0.01018060418221126</v>
       </c>
       <c r="D24">
-        <v>0.1599697295186018</v>
+        <v>1.052031594136857</v>
       </c>
       <c r="E24">
-        <v>0.03172663874979914</v>
+        <v>-0.08596953611332776</v>
       </c>
       <c r="F24">
-        <v>0.7179982878382851</v>
+        <v>0.3270187824905088</v>
       </c>
       <c r="G24">
-        <v>0.005484011592264122</v>
+        <v>0.0103477624373652</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>0.4199761579272857</v>
+        <v>-0.2816275537328172</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>0.002121010864625627</v>
+        <v>-0.008843047939070437</v>
       </c>
       <c r="D25">
-        <v>-0.1432552159619829</v>
+        <v>0.2631085288980025</v>
       </c>
       <c r="E25">
-        <v>0.05452878180109828</v>
+        <v>-0.09697362761972285</v>
       </c>
       <c r="F25">
-        <v>0.5346051380613122</v>
+        <v>0.2686595959047965</v>
       </c>
       <c r="G25">
-        <v>0.003406424727791379</v>
+        <v>0.007960218180268834</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>0.1345972073039742</v>
+        <v>-0.8953307511202248</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1278,25 +1278,25 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>0.002227473735394299</v>
+        <v>-0.008546644195499154</v>
       </c>
       <c r="D26">
-        <v>0.04678084551204853</v>
+        <v>0.5643001443001442</v>
       </c>
       <c r="E26">
-        <v>0.05470839099617777</v>
+        <v>-0.09213519616251464</v>
       </c>
       <c r="F26">
-        <v>0.5332581496792461</v>
+        <v>0.2933865286249726</v>
       </c>
       <c r="G26">
-        <v>0.003565628362121604</v>
+        <v>0.008101159348792934</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>0.3385799048487017</v>
+        <v>-0.5553102453102451</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1307,257 +1307,257 @@
         <v>34</v>
       </c>
       <c r="C27">
-        <v>0.003274380371966896</v>
+        <v>-0.00847017787355272</v>
       </c>
       <c r="D27">
-        <v>-0.1134320514489689</v>
+        <v>0.3657814992025518</v>
       </c>
       <c r="E27">
-        <v>0.09961393423104674</v>
+        <v>-0.09488751239699358</v>
       </c>
       <c r="F27">
-        <v>0.2557805293148222</v>
+        <v>0.2791416267732263</v>
       </c>
       <c r="G27">
-        <v>0.002868612319989333</v>
+        <v>0.007793774264445016</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>0.3155117772786946</v>
+        <v>-0.7438118022328547</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28">
-        <v>0.004234478334231535</v>
+        <v>-0.007533137145431238</v>
       </c>
       <c r="D28">
-        <v>-0.3253543626381973</v>
+        <v>0.3203144224196855</v>
       </c>
       <c r="E28">
-        <v>0.118481991579655</v>
+        <v>-0.08101218219509221</v>
       </c>
       <c r="F28">
-        <v>0.1760305651478831</v>
+        <v>0.3557855607836922</v>
       </c>
       <c r="G28">
-        <v>0.003112475816687231</v>
+        <v>0.00812875508057659</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>0.2293622991461337</v>
+        <v>-0.6665265436318066</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>0.00543648826636831</v>
+        <v>-0.007296911605871024</v>
       </c>
       <c r="D29">
-        <v>-0.2653143681715109</v>
+        <v>0.5915588212956632</v>
       </c>
       <c r="E29">
-        <v>0.1256787930712719</v>
+        <v>-0.0676901760976367</v>
       </c>
       <c r="F29">
-        <v>0.1510291488314281</v>
+        <v>0.440594835898683</v>
       </c>
       <c r="G29">
-        <v>0.003763808562288196</v>
+        <v>0.009432884543978446</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>0.4468655947227376</v>
+        <v>-0.364336599073441</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30">
-        <v>0.005624483658834806</v>
+        <v>-0.007208574872295239</v>
       </c>
       <c r="D30">
-        <v>0.02514430014430002</v>
+        <v>0.3112778157514998</v>
       </c>
       <c r="E30">
-        <v>0.1113713013056608</v>
+        <v>-0.07428721316510957</v>
       </c>
       <c r="F30">
-        <v>0.2036049386959605</v>
+        <v>0.397247191851984</v>
       </c>
       <c r="G30">
-        <v>0.004401771005781312</v>
+        <v>0.008487152497947195</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>0.7619516594516595</v>
+        <v>-0.6330454925191765</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31">
-        <v>0.005715958504370371</v>
+        <v>-0.006362784128955285</v>
       </c>
       <c r="D31">
-        <v>-0.4138758015167788</v>
+        <v>0.5036815523657633</v>
       </c>
       <c r="E31">
-        <v>0.1309663774336815</v>
+        <v>-0.06326797040896187</v>
       </c>
       <c r="F31">
-        <v>0.134436806509809</v>
+        <v>0.4710925880531842</v>
       </c>
       <c r="G31">
-        <v>0.003794903291426277</v>
+        <v>0.008802796478208287</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>0.3349147625557399</v>
+        <v>-0.329843168527379</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>39</v>
       </c>
       <c r="C32">
-        <v>0.005864248270622028</v>
+        <v>-0.005774124763678806</v>
       </c>
       <c r="D32">
-        <v>-0.6143634926059738</v>
+        <v>1.310856687172477</v>
       </c>
       <c r="E32">
-        <v>0.1348171522142589</v>
+        <v>-0.04798257214581907</v>
       </c>
       <c r="F32">
-        <v>0.1232573760803011</v>
+        <v>0.5848258452730246</v>
       </c>
       <c r="G32">
-        <v>0.003780179471259441</v>
+        <v>0.01054218036101107</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.1538530308455119</v>
+        <v>0.5544463431305533</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33">
-        <v>0.005974166977868981</v>
+        <v>-0.005590381227183154</v>
       </c>
       <c r="D33">
-        <v>-0.005079582072063271</v>
+        <v>0.5658669400774663</v>
       </c>
       <c r="E33">
-        <v>0.1075331571330563</v>
+        <v>-0.05661483284946889</v>
       </c>
       <c r="F33">
-        <v>0.2197198923828984</v>
+        <v>0.5190660418905833</v>
       </c>
       <c r="G33">
-        <v>0.004844374368207867</v>
+        <v>0.008646540750896197</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>0.7775362920287733</v>
+        <v>-0.1664730006835269</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
       <c r="C34">
-        <v>0.006894077291970883</v>
+        <v>-0.004858424687673381</v>
       </c>
       <c r="D34">
-        <v>-0.2369769255389558</v>
+        <v>-0.1131620718462824</v>
       </c>
       <c r="E34">
-        <v>0.1565924467007339</v>
+        <v>-0.05028627446063404</v>
       </c>
       <c r="F34">
-        <v>0.072960565904719</v>
+        <v>0.5669069535829185</v>
       </c>
       <c r="G34">
-        <v>0.003813665350907036</v>
+        <v>0.008463003874197104</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>0.6661471997092299</v>
+        <v>-0.7496157059314953</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>42</v>
       </c>
       <c r="C35">
-        <v>0.007110440856279687</v>
+        <v>-0.004253129353571299</v>
       </c>
       <c r="D35">
-        <v>0.6013539666265233</v>
+        <v>0.1732516898306372</v>
       </c>
       <c r="E35">
-        <v>0.09678099410632912</v>
+        <v>-0.04595617504494649</v>
       </c>
       <c r="F35">
-        <v>0.2696161643034252</v>
+        <v>0.6007996245936418</v>
       </c>
       <c r="G35">
-        <v>0.006413443384504474</v>
+        <v>0.00810837725777944</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>1.532821718799162</v>
+        <v>-0.3839082554872029</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1568,25 +1568,25 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>0.007597772499554627</v>
+        <v>-0.00416648839308542</v>
       </c>
       <c r="D36">
-        <v>-0.6897221001638295</v>
+        <v>-0.1446707678286626</v>
       </c>
       <c r="E36">
-        <v>0.1845191550175796</v>
+        <v>-0.04441873803337287</v>
       </c>
       <c r="F36">
-        <v>0.03417316609303446</v>
+        <v>0.6130474032960573</v>
       </c>
       <c r="G36">
-        <v>0.003549368397994585</v>
+        <v>0.00821870560753621</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>0.3055860972778266</v>
+        <v>-0.6904807473228526</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1597,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>0.00837641093911541</v>
+        <v>-0.003983336203103178</v>
       </c>
       <c r="D37">
-        <v>-0.5659979901051329</v>
+        <v>0.05088326877800561</v>
       </c>
       <c r="E37">
-        <v>0.2027187199765365</v>
+        <v>-0.04324937646401993</v>
       </c>
       <c r="F37">
-        <v>0.01974453810043698</v>
+        <v>0.6224352481190312</v>
       </c>
       <c r="G37">
-        <v>0.0035487896898283</v>
+        <v>0.008070285160858609</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>0.5313118429189858</v>
+        <v>-0.4709337738285106</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>0.008445805638812009</v>
+        <v>-0.002536824364867758</v>
       </c>
       <c r="D38">
-        <v>-0.4123245478414652</v>
+        <v>0.1036367433735856</v>
       </c>
       <c r="E38">
-        <v>0.1584306990032458</v>
+        <v>-0.02425375525263773</v>
       </c>
       <c r="F38">
-        <v>0.06961697088906185</v>
+        <v>0.782513731512502</v>
       </c>
       <c r="G38">
-        <v>0.00461647023548464</v>
+        <v>0.009170900044935501</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>0.6940759908429079</v>
+        <v>-0.2286872484240907</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,286 +1655,286 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>0.009173080167455418</v>
+        <v>-0.002171598322663004</v>
       </c>
       <c r="D39">
-        <v>-0.7298013974329763</v>
+        <v>-0.1676592997645631</v>
       </c>
       <c r="E39">
-        <v>0.2098542969503866</v>
+        <v>-0.02287018666719404</v>
       </c>
       <c r="F39">
-        <v>0.01573233573132586</v>
+        <v>0.794637512402627</v>
       </c>
       <c r="G39">
-        <v>0.003748398657240761</v>
+        <v>0.008325771824072325</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>0.4718721045036834</v>
+        <v>-0.4521386800334167</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.01048157719569072</v>
+        <v>-0.00105110973130258</v>
       </c>
       <c r="D40">
-        <v>-0.5002987175731535</v>
+        <v>0.0694790005316321</v>
       </c>
       <c r="E40">
-        <v>0.2169214172187592</v>
+        <v>-0.01093319392643337</v>
       </c>
       <c r="F40">
-        <v>0.01247708386943506</v>
+        <v>0.900981299611776</v>
       </c>
       <c r="G40">
-        <v>0.004137009024330737</v>
+        <v>0.00843147139780326</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.8727878950623311</v>
+        <v>-0.06821637426900583</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.01060797844467419</v>
+        <v>0.0001342791399038933</v>
       </c>
       <c r="D41">
-        <v>-0.3389360441146155</v>
+        <v>-0.2469518493202707</v>
       </c>
       <c r="E41">
-        <v>0.2253384473741545</v>
+        <v>0.0014645010602182</v>
       </c>
       <c r="F41">
-        <v>0.009381798728607732</v>
+        <v>0.9867032230441799</v>
       </c>
       <c r="G41">
-        <v>0.004022626275545752</v>
+        <v>0.008041678724747094</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>1.050709132137704</v>
+        <v>-0.2293612819928607</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.01156042492967822</v>
+        <v>0.0004385617061390447</v>
       </c>
       <c r="D42">
-        <v>-0.7977958559819462</v>
+        <v>0.1131176425913269</v>
       </c>
       <c r="E42">
-        <v>0.2869514459245406</v>
+        <v>0.004762631325125302</v>
       </c>
       <c r="F42">
-        <v>0.0008502191075069178</v>
+        <v>0.9567771485907296</v>
       </c>
       <c r="G42">
-        <v>0.003384810325043052</v>
+        <v>0.008076201424654312</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.7166198098059</v>
+        <v>0.1705692260955418</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.01189358626316957</v>
+        <v>0.0005090276002288876</v>
       </c>
       <c r="D43">
-        <v>-0.6919799363126431</v>
+        <v>-0.06440191387559815</v>
       </c>
       <c r="E43">
-        <v>0.2511344624576495</v>
+        <v>0.005695267579983086</v>
       </c>
       <c r="F43">
-        <v>0.003677566564835567</v>
+        <v>0.9483238370335378</v>
       </c>
       <c r="G43">
-        <v>0.004020580415333301</v>
+        <v>0.007838780039945155</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.8660798641625709</v>
+        <v>0.002280701754386133</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.01234731954800255</v>
+        <v>0.001085312170085171</v>
       </c>
       <c r="D44">
-        <v>-0.3652519556466923</v>
+        <v>-0.1870475431001746</v>
       </c>
       <c r="E44">
-        <v>0.2284250647626276</v>
+        <v>0.01117408960770358</v>
       </c>
       <c r="F44">
-        <v>0.0084294247962766</v>
+        <v>0.8988110525306678</v>
       </c>
       <c r="G44">
-        <v>0.004615520083705187</v>
+        <v>0.008518119575519264</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>1.252246905141642</v>
+        <v>-0.04487164881901717</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.01275551449258618</v>
+        <v>0.003068992745569683</v>
       </c>
       <c r="D45">
-        <v>-0.6719706869988825</v>
+        <v>-0.3994281157439051</v>
       </c>
       <c r="E45">
-        <v>0.3226940244924875</v>
+        <v>0.03533415160762548</v>
       </c>
       <c r="F45">
-        <v>0.0001608594655749094</v>
+        <v>0.6875199289598901</v>
       </c>
       <c r="G45">
-        <v>0.003281387582792396</v>
+        <v>0.00761304223899975</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>0.9990017115299069</v>
+        <v>0.00260993392572334</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.01330615530846547</v>
+        <v>0.003142937148561898</v>
       </c>
       <c r="D46">
-        <v>-0.6796529201792358</v>
+        <v>-0.3228825852510063</v>
       </c>
       <c r="E46">
-        <v>0.3014904785998598</v>
+        <v>0.03315073368575434</v>
       </c>
       <c r="F46">
-        <v>0.0004430354027214837</v>
+        <v>0.7059104565168808</v>
       </c>
       <c r="G46">
-        <v>0.003690744435609287</v>
+        <v>0.008310594758107295</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>1.063453425229741</v>
+        <v>0.08884218121060233</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.01348282411689976</v>
+        <v>0.003751076163691671</v>
       </c>
       <c r="D47">
-        <v>-0.8269597559917109</v>
+        <v>-0.02269043821675387</v>
       </c>
       <c r="E47">
-        <v>0.3301824030285961</v>
+        <v>0.03769350938171841</v>
       </c>
       <c r="F47">
-        <v>0.000110436710129893</v>
+        <v>0.6678511613257861</v>
       </c>
       <c r="G47">
-        <v>0.003380563862466291</v>
+        <v>0.008721855564595826</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.9392902033221581</v>
+        <v>0.4687005392268551</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.01416453670112627</v>
+        <v>0.005211789014521032</v>
       </c>
       <c r="D48">
-        <v>-0.8346278032744199</v>
+        <v>-0.4692762208551681</v>
       </c>
       <c r="E48">
-        <v>0.2938210239787692</v>
+        <v>0.0573049910593025</v>
       </c>
       <c r="F48">
-        <v>0.0006275072641161833</v>
+        <v>0.5139762563325767</v>
       </c>
       <c r="G48">
-        <v>0.00404149758687118</v>
+        <v>0.00796358180938401</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>1.020926504573121</v>
+        <v>0.2134681400470871</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1945,25 +1945,25 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.01666616135113237</v>
+        <v>0.005483956247315029</v>
       </c>
       <c r="D49">
-        <v>-1.185934614675216</v>
+        <v>-0.6296536796536798</v>
       </c>
       <c r="E49">
-        <v>0.4113371602018348</v>
+        <v>0.05990242433949355</v>
       </c>
       <c r="F49">
-        <v>9.602299888618754E-07</v>
+        <v>0.4950532852728974</v>
       </c>
       <c r="G49">
-        <v>0.003239027679592398</v>
+        <v>0.008014885360552402</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.9973325223231237</v>
+        <v>0.08874458874458901</v>
       </c>
     </row>
   </sheetData>

--- a/output/palmer_drought_trendlines/state/Year.xlsx
+++ b/output/palmer_drought_trendlines/state/Year.xlsx
@@ -52,12 +52,12 @@
     <t>Utah</t>
   </si>
   <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
     <t>California</t>
   </si>
   <si>
-    <t>Wyoming</t>
-  </si>
-  <si>
     <t>Nevada</t>
   </si>
   <si>
@@ -124,12 +124,12 @@
     <t>Pennsylvania</t>
   </si>
   <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
     <t>Kansas</t>
   </si>
   <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
     <t>Minnesota</t>
   </si>
   <si>
@@ -172,19 +172,19 @@
     <t>Illinois</t>
   </si>
   <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
     <t>Iowa</t>
   </si>
   <si>
+    <t>Vermont</t>
+  </si>
+  <si>
     <t>Indiana</t>
-  </si>
-  <si>
-    <t>Vermont</t>
   </si>
 </sst>
 </file>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.0350917282797556</v>
+        <v>-0.02443952960124114</v>
       </c>
       <c r="D2">
-        <v>1.714998101313891</v>
+        <v>1.253402825244931</v>
       </c>
       <c r="E2">
-        <v>-0.3092330069513365</v>
+        <v>-0.319507714332238</v>
       </c>
       <c r="F2">
-        <v>0.0003087215118444015</v>
+        <v>0.0001882220338951596</v>
       </c>
       <c r="G2">
-        <v>0.009465019212448085</v>
+        <v>0.006357075771787097</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-2.882018303334093</v>
+        <v>-1.948175552517658</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.03441514960197162</v>
+        <v>-0.02374984998930359</v>
       </c>
       <c r="D3">
-        <v>1.955555935292778</v>
+        <v>1.493392952077163</v>
       </c>
       <c r="E3">
-        <v>-0.294177350759346</v>
+        <v>-0.2925820885030132</v>
       </c>
       <c r="F3">
-        <v>0.0006175706680827408</v>
+        <v>0.0006632117562769973</v>
       </c>
       <c r="G3">
-        <v>0.009806486746986792</v>
+        <v>0.006807827638431206</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-2.552828662565505</v>
+        <v>-1.617837396521607</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,83 +640,83 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.03315620766002445</v>
+        <v>-0.02272558565045507</v>
       </c>
       <c r="D4">
-        <v>1.823903318903319</v>
+        <v>1.371909698488646</v>
       </c>
       <c r="E4">
-        <v>-0.2733430080875031</v>
+        <v>-0.2670402501120929</v>
       </c>
       <c r="F4">
-        <v>0.001517991739923782</v>
+        <v>0.001966210224825782</v>
       </c>
       <c r="G4">
-        <v>0.01023346333108652</v>
+        <v>0.00719286568402867</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-2.519559884559885</v>
+        <v>-1.605142021720969</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.03207462619073708</v>
+        <v>-0.02151657335566536</v>
       </c>
       <c r="D5">
-        <v>1.576973874079138</v>
+        <v>1.347858282068808</v>
       </c>
       <c r="E5">
-        <v>-0.304808404870169</v>
+        <v>-0.2356719729473545</v>
       </c>
       <c r="F5">
-        <v>0.0003799627420766842</v>
+        <v>0.006521487779456427</v>
       </c>
       <c r="G5">
-        <v>0.008789994807055682</v>
+        <v>0.007781888168737166</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-2.62480215690742</v>
+        <v>-1.470812827523354</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.0320594077142892</v>
+        <v>-0.02105503175009001</v>
       </c>
       <c r="D6">
-        <v>1.804714437609175</v>
+        <v>1.099458114984431</v>
       </c>
       <c r="E6">
-        <v>-0.2563516008142526</v>
+        <v>-0.3075506199452243</v>
       </c>
       <c r="F6">
-        <v>0.003007328332491556</v>
+        <v>0.0003342109078227538</v>
       </c>
       <c r="G6">
-        <v>0.01060198553012712</v>
+        <v>0.005713350773657829</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-2.39506797296271</v>
+        <v>-1.65875104427736</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -727,25 +727,25 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.03136115792604342</v>
+        <v>-0.02086446163987345</v>
       </c>
       <c r="D7">
-        <v>1.388903318903318</v>
+        <v>0.9340464798359533</v>
       </c>
       <c r="E7">
-        <v>-0.259986870084001</v>
+        <v>-0.2443912385717085</v>
       </c>
       <c r="F7">
-        <v>0.002607673479933152</v>
+        <v>0.004741496539451947</v>
       </c>
       <c r="G7">
-        <v>0.01021578443127013</v>
+        <v>0.007260672359759121</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-2.719408369408369</v>
+        <v>-1.799197994987469</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -756,25 +756,25 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.02800987548677384</v>
+        <v>-0.01766640316961731</v>
       </c>
       <c r="D8">
-        <v>1.543232702969545</v>
+        <v>1.095015569226096</v>
       </c>
       <c r="E8">
-        <v>-0.2365335952691653</v>
+        <v>-0.22091100074049</v>
       </c>
       <c r="F8">
-        <v>0.006322359021224115</v>
+        <v>0.01091326831483686</v>
       </c>
       <c r="G8">
-        <v>0.01009124138617706</v>
+        <v>0.006840607270983772</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-2.126060985797828</v>
+        <v>-1.219283245993772</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -785,25 +785,25 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.02692457201296092</v>
+        <v>-0.01566688233421861</v>
       </c>
       <c r="D9">
-        <v>1.762978658768132</v>
+        <v>1.275145439355966</v>
       </c>
       <c r="E9">
-        <v>-0.2505077275860475</v>
+        <v>-0.2123051935486894</v>
       </c>
       <c r="F9">
-        <v>0.003766514290194253</v>
+        <v>0.01452827951913731</v>
       </c>
       <c r="G9">
-        <v>0.009126048545820295</v>
+        <v>0.006324632000326245</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.764140274929749</v>
+        <v>-0.7772161464266727</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,25 +814,25 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.02254352919077708</v>
+        <v>-0.01182696505316031</v>
       </c>
       <c r="D10">
-        <v>1.098747626642363</v>
+        <v>0.6343631806789699</v>
       </c>
       <c r="E10">
-        <v>-0.2254473416057909</v>
+        <v>-0.2153481591643338</v>
       </c>
       <c r="F10">
-        <v>0.009346649241382555</v>
+        <v>0.01314571441631232</v>
       </c>
       <c r="G10">
-        <v>0.00854432801571225</v>
+        <v>0.00470380518440593</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-1.854454697349434</v>
+        <v>-0.9149692412850304</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -843,25 +843,25 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.02048946968392529</v>
+        <v>-0.009593479708987942</v>
       </c>
       <c r="D11">
-        <v>1.035822890559733</v>
+        <v>0.5636633249791143</v>
       </c>
       <c r="E11">
-        <v>-0.2149599378873998</v>
+        <v>-0.195906949965356</v>
       </c>
       <c r="F11">
-        <v>0.01331544747771309</v>
+        <v>0.02436951986954137</v>
       </c>
       <c r="G11">
-        <v>0.008164477618906351</v>
+        <v>0.004211690906183774</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-1.64829763803448</v>
+        <v>-0.6930825168983061</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -872,25 +872,25 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.01781811398725822</v>
+        <v>-0.006922124012320876</v>
       </c>
       <c r="D12">
-        <v>0.6535258601048074</v>
+        <v>0.1813662945241891</v>
       </c>
       <c r="E12">
-        <v>-0.1836691149431781</v>
+        <v>-0.130982452713145</v>
       </c>
       <c r="F12">
-        <v>0.03502274579688019</v>
+        <v>0.1343885787538717</v>
       </c>
       <c r="G12">
-        <v>0.008363772195419665</v>
+        <v>0.004595119258248659</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-1.680647072226019</v>
+        <v>-0.7254319510898457</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,25 +901,25 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.01742805139149052</v>
+        <v>-0.006528643781556595</v>
       </c>
       <c r="D13">
-        <v>0.7155525176577808</v>
+        <v>0.2432448545606438</v>
       </c>
       <c r="E13">
-        <v>-0.1825687841851854</v>
+        <v>-0.1313293694090276</v>
       </c>
       <c r="F13">
-        <v>0.03614888596134367</v>
+        <v>0.1333510059110063</v>
       </c>
       <c r="G13">
-        <v>0.008231698343545112</v>
+        <v>0.00432226647149083</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-1.567522214627478</v>
+        <v>-0.6120074808232702</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,25 +930,25 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.01710592407458619</v>
+        <v>-0.006220187004638591</v>
       </c>
       <c r="D14">
-        <v>0.7026855016328704</v>
+        <v>0.2309702286018075</v>
       </c>
       <c r="E14">
-        <v>-0.1804365190283077</v>
+        <v>-0.1291772557497342</v>
       </c>
       <c r="F14">
-        <v>0.03841812465724645</v>
+        <v>0.1398874746250019</v>
       </c>
       <c r="G14">
-        <v>0.008178300072744185</v>
+        <v>0.004187855170552282</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-1.538190552137921</v>
+        <v>-0.5838742690058479</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -959,25 +959,25 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.01678692741569399</v>
+        <v>-0.005799800507514448</v>
       </c>
       <c r="D15">
-        <v>0.5974982911825019</v>
+        <v>0.1213894584947216</v>
       </c>
       <c r="E15">
-        <v>-0.168565848745834</v>
+        <v>-0.09855447480334635</v>
       </c>
       <c r="F15">
-        <v>0.05334676505950871</v>
+        <v>0.2608965499461713</v>
       </c>
       <c r="G15">
-        <v>0.008609352094543396</v>
+        <v>0.005136243136100135</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-1.601589200273411</v>
+        <v>-0.6383844079896711</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -988,25 +988,25 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.01654527540224607</v>
+        <v>-0.005607704201516976</v>
       </c>
       <c r="D16">
-        <v>0.8440943267259058</v>
+        <v>0.3701329080276448</v>
       </c>
       <c r="E16">
-        <v>-0.1770043513174329</v>
+        <v>-0.1222657101524439</v>
       </c>
       <c r="F16">
-        <v>0.04232159730840781</v>
+        <v>0.1625305524179091</v>
       </c>
       <c r="G16">
-        <v>0.0080687486196152</v>
+        <v>0.003992437494781704</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-1.32333675096833</v>
+        <v>-0.3644763423710791</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,25 +1017,25 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.01511925198144563</v>
+        <v>-0.00412244177410911</v>
       </c>
       <c r="D17">
-        <v>0.6018261562998406</v>
+        <v>0.1252977139819245</v>
       </c>
       <c r="E17">
-        <v>-0.1587048136349985</v>
+        <v>-0.08082787750798495</v>
       </c>
       <c r="F17">
-        <v>0.06912921019146151</v>
+        <v>0.3568845978914853</v>
       </c>
       <c r="G17">
-        <v>0.008249528688465213</v>
+        <v>0.004458598550916217</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-1.378795853269537</v>
+        <v>-0.4147421584263689</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1046,25 +1046,25 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.01495773611683615</v>
+        <v>-0.003849852772110709</v>
       </c>
       <c r="D18">
-        <v>0.5794539378749903</v>
+        <v>0.09811232627022115</v>
       </c>
       <c r="E18">
-        <v>-0.1609673931508142</v>
+        <v>-0.07901047614498505</v>
       </c>
       <c r="F18">
-        <v>0.06520827822414346</v>
+        <v>0.3678349684642644</v>
       </c>
       <c r="G18">
-        <v>0.008043697151658057</v>
+        <v>0.004260179928442388</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-1.380009493430546</v>
+        <v>-0.4062183868762816</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1075,25 +1075,25 @@
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.01477625361112705</v>
+        <v>-0.003659256573077384</v>
       </c>
       <c r="D19">
-        <v>0.5191577428419532</v>
+        <v>0.03742120452646763</v>
       </c>
       <c r="E19">
-        <v>-0.1528105056046239</v>
+        <v>-0.06547493790231257</v>
       </c>
       <c r="F19">
-        <v>0.08024794653065741</v>
+        <v>0.4557303403146232</v>
       </c>
       <c r="G19">
-        <v>0.008381247994061201</v>
+        <v>0.004891174824341427</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-1.416531480215691</v>
+        <v>-0.4419414065466697</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1104,25 +1104,25 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.01426857393309784</v>
+        <v>-0.003177778763355303</v>
       </c>
       <c r="D20">
-        <v>0.5758794714057871</v>
+        <v>0.09527834738361074</v>
       </c>
       <c r="E20">
-        <v>-0.1564651429664039</v>
+        <v>-0.07090070832728665</v>
       </c>
       <c r="F20">
-        <v>0.07319684609158181</v>
+        <v>0.4191730436859838</v>
       </c>
       <c r="G20">
-        <v>0.007899672424783066</v>
+        <v>0.003921092392203651</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-1.293303713830029</v>
+        <v>-0.3210106706159339</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1133,25 +1133,25 @@
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.01389920846529927</v>
+        <v>-0.003080684883617788</v>
       </c>
       <c r="D21">
-        <v>0.3708779524568999</v>
+        <v>-0.09792473608263083</v>
       </c>
       <c r="E21">
-        <v>-0.1169134233669247</v>
+        <v>-0.03585143982371949</v>
       </c>
       <c r="F21">
-        <v>0.1818631029711424</v>
+        <v>0.6831890655797477</v>
       </c>
       <c r="G21">
-        <v>0.01035536501832537</v>
+        <v>0.007531642804213543</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-1.449918356497304</v>
+        <v>-0.501494455836561</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1162,25 +1162,25 @@
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.01293594847632614</v>
+        <v>-0.001928315758167104</v>
       </c>
       <c r="D22">
-        <v>0.655435938330675</v>
+        <v>0.1784385205437836</v>
       </c>
       <c r="E22">
-        <v>-0.1377497579237138</v>
+        <v>-0.04022046958846864</v>
       </c>
       <c r="F22">
-        <v>0.1152356958748268</v>
+        <v>0.6470327213440895</v>
       </c>
       <c r="G22">
-        <v>0.008157851491909651</v>
+        <v>0.004201532979116732</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-1.039173312068049</v>
+        <v>-0.07417084377610697</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,25 +1191,25 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>-0.01193869475910457</v>
+        <v>-0.0007214470944884746</v>
       </c>
       <c r="D23">
-        <v>1.286327941064783</v>
+        <v>0.8002472089314193</v>
       </c>
       <c r="E23">
-        <v>-0.1062923615365886</v>
+        <v>-0.009120488276812446</v>
       </c>
       <c r="F23">
-        <v>0.2251180339239412</v>
+        <v>0.9173344628227655</v>
       </c>
       <c r="G23">
-        <v>0.00979525639216423</v>
+        <v>0.006937398775345117</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.277641072377915</v>
+        <v>0.7057376395534292</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1220,25 +1220,25 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>-0.01018060418221126</v>
+        <v>0.0006071606845009857</v>
       </c>
       <c r="D24">
-        <v>1.052031594136857</v>
+        <v>0.5845617832459934</v>
       </c>
       <c r="E24">
-        <v>-0.08596953611332776</v>
+        <v>0.007301736965992302</v>
       </c>
       <c r="F24">
-        <v>0.3270187824905088</v>
+        <v>0.9337769771414238</v>
       </c>
       <c r="G24">
-        <v>0.0103477624373652</v>
+        <v>0.007292798330333093</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.2816275537328172</v>
+        <v>0.6640998329156225</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1249,25 +1249,25 @@
         <v>32</v>
       </c>
       <c r="C25">
-        <v>-0.008843047939070437</v>
+        <v>0.002252873683166974</v>
       </c>
       <c r="D25">
-        <v>0.2631085288980025</v>
+        <v>-0.2177147413989519</v>
       </c>
       <c r="E25">
-        <v>-0.09697362761972285</v>
+        <v>0.05033025202652446</v>
       </c>
       <c r="F25">
-        <v>0.2686595959047965</v>
+        <v>0.566567428388574</v>
       </c>
       <c r="G25">
-        <v>0.007960218180268834</v>
+        <v>0.003920895788908229</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>-0.8953307511202248</v>
+        <v>0.07741171109592165</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1278,25 +1278,25 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>-0.008546644195499154</v>
+        <v>0.002618769338335431</v>
       </c>
       <c r="D26">
-        <v>0.5643001443001442</v>
+        <v>0.08046555783397877</v>
       </c>
       <c r="E26">
-        <v>-0.09213519616251464</v>
+        <v>0.0544049405622922</v>
       </c>
       <c r="F26">
-        <v>0.2933865286249726</v>
+        <v>0.5355348790996669</v>
       </c>
       <c r="G26">
-        <v>0.008101159348792934</v>
+        <v>0.004215446136141237</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>-0.5553102453102451</v>
+        <v>0.4235243411559202</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1307,25 +1307,25 @@
         <v>34</v>
       </c>
       <c r="C27">
-        <v>-0.00847017787355272</v>
+        <v>0.002753335455223763</v>
       </c>
       <c r="D27">
-        <v>0.3657814992025518</v>
+        <v>-0.1205707450444293</v>
       </c>
       <c r="E27">
-        <v>-0.09488751239699358</v>
+        <v>0.06384971460761024</v>
       </c>
       <c r="F27">
-        <v>0.2791416267732263</v>
+        <v>0.4670159960142748</v>
       </c>
       <c r="G27">
-        <v>0.007793774264445016</v>
+        <v>0.003774343465467564</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>-0.7438118022328547</v>
+        <v>0.2401161995898837</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1336,83 +1336,83 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>-0.007533137145431238</v>
+        <v>0.003646516534222441</v>
       </c>
       <c r="D28">
-        <v>0.3203144224196855</v>
+        <v>-0.1641372370319739</v>
       </c>
       <c r="E28">
-        <v>-0.08101218219509221</v>
+        <v>0.07371597973951861</v>
       </c>
       <c r="F28">
-        <v>0.3557855607836922</v>
+        <v>0.4008969198158178</v>
       </c>
       <c r="G28">
-        <v>0.00812875508057659</v>
+        <v>0.004326748613752474</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>-0.6665265436318066</v>
+        <v>0.3135564289511659</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>-0.007296911605871024</v>
+        <v>0.003823550896672633</v>
       </c>
       <c r="D29">
-        <v>0.5915588212956632</v>
+        <v>-0.1667809675704413</v>
       </c>
       <c r="E29">
-        <v>-0.0676901760976367</v>
+        <v>0.07062397106241391</v>
       </c>
       <c r="F29">
-        <v>0.440594835898683</v>
+        <v>0.4209953322287456</v>
       </c>
       <c r="G29">
-        <v>0.009432884543978446</v>
+        <v>0.004736497154493112</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>-0.364336599073441</v>
+        <v>0.3341041998936736</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30">
-        <v>-0.007208574872295239</v>
+        <v>0.003910652759588075</v>
       </c>
       <c r="D30">
-        <v>0.3112778157514998</v>
+        <v>0.1058976987924356</v>
       </c>
       <c r="E30">
-        <v>-0.07428721316510957</v>
+        <v>0.05333092686151214</v>
       </c>
       <c r="F30">
-        <v>0.397247191851984</v>
+        <v>0.5436316831145562</v>
       </c>
       <c r="G30">
-        <v>0.008487152497947195</v>
+        <v>0.006422142827264379</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>-0.6330454925191765</v>
+        <v>0.6181932102984735</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1423,25 +1423,25 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>-0.006362784128955285</v>
+        <v>0.004815160733200106</v>
       </c>
       <c r="D31">
-        <v>0.5036815523657633</v>
+        <v>0.01930394167236293</v>
       </c>
       <c r="E31">
-        <v>-0.06326797040896187</v>
+        <v>0.07788398986979024</v>
       </c>
       <c r="F31">
-        <v>0.4710925880531842</v>
+        <v>0.3747250558103592</v>
       </c>
       <c r="G31">
-        <v>0.008802796478208287</v>
+        <v>0.00540592122450631</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>-0.329843168527379</v>
+        <v>0.6500899977215768</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1452,25 +1452,25 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>-0.005774124763678806</v>
+        <v>0.00532749291688625</v>
       </c>
       <c r="D32">
-        <v>1.310856687172477</v>
+        <v>0.8297865876813243</v>
       </c>
       <c r="E32">
-        <v>-0.04798257214581907</v>
+        <v>0.06048994834850909</v>
       </c>
       <c r="F32">
-        <v>0.5848258452730246</v>
+        <v>0.4908246332008135</v>
       </c>
       <c r="G32">
-        <v>0.01054218036101107</v>
+        <v>0.00771031257861862</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.5544463431305533</v>
+        <v>1.527688159793423</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1481,25 +1481,25 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>-0.005590381227183154</v>
+        <v>0.005618891955774235</v>
       </c>
       <c r="D33">
-        <v>0.5658669400774663</v>
+        <v>0.08013176881597955</v>
       </c>
       <c r="E33">
-        <v>-0.05661483284946889</v>
+        <v>0.09523953580407023</v>
       </c>
       <c r="F33">
-        <v>0.5190660418905833</v>
+        <v>0.2773538133111108</v>
       </c>
       <c r="G33">
-        <v>0.008646540750896197</v>
+        <v>0.005150899764921861</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>-0.1664730006835269</v>
+        <v>0.8162066150224043</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1510,25 +1510,25 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>-0.004858424687673381</v>
+        <v>0.00635996218860823</v>
       </c>
       <c r="D34">
-        <v>-0.1131620718462824</v>
+        <v>-0.5992921698184855</v>
       </c>
       <c r="E34">
-        <v>-0.05028627446063404</v>
+        <v>0.1107344801495361</v>
       </c>
       <c r="F34">
-        <v>0.5669069535829185</v>
+        <v>0.2062181621944746</v>
       </c>
       <c r="G34">
-        <v>0.008463003874197104</v>
+        <v>0.005006345752625806</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>-0.7496157059314953</v>
+        <v>0.2338628768891926</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,25 +1539,25 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>-0.004253129353571299</v>
+        <v>0.007062090514280148</v>
       </c>
       <c r="D35">
-        <v>0.1732516898306372</v>
+        <v>-0.3170745044429255</v>
       </c>
       <c r="E35">
-        <v>-0.04595617504494649</v>
+        <v>0.1382643956009903</v>
       </c>
       <c r="F35">
-        <v>0.6007996245936418</v>
+        <v>0.1138708189620946</v>
       </c>
       <c r="G35">
-        <v>0.00810837725777944</v>
+        <v>0.004436697696716069</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>-0.3839082554872029</v>
+        <v>0.608059352927774</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1568,25 +1568,25 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>-0.00416648839308542</v>
+        <v>0.007095188526486235</v>
       </c>
       <c r="D36">
-        <v>-0.1446707678286626</v>
+        <v>-0.6326767676767676</v>
       </c>
       <c r="E36">
-        <v>-0.04441873803337287</v>
+        <v>0.1330602953166608</v>
       </c>
       <c r="F36">
-        <v>0.6130474032960573</v>
+        <v>0.128265414963233</v>
       </c>
       <c r="G36">
-        <v>0.00821870560753621</v>
+        <v>0.004635160083236166</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>-0.6904807473228526</v>
+        <v>0.2967929292929292</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1597,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>-0.003983336203103178</v>
+        <v>0.007179229301567589</v>
       </c>
       <c r="D37">
-        <v>0.05088326877800561</v>
+        <v>-0.432827903091061</v>
       </c>
       <c r="E37">
-        <v>-0.04324937646401993</v>
+        <v>0.1509326740077831</v>
       </c>
       <c r="F37">
-        <v>0.6224352481190312</v>
+        <v>0.08407754385527072</v>
       </c>
       <c r="G37">
-        <v>0.008070285160858609</v>
+        <v>0.004124002371037225</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>-0.4709337738285106</v>
+        <v>0.5076511354142932</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>-0.002536824364867758</v>
+        <v>0.008431505550830578</v>
       </c>
       <c r="D38">
-        <v>0.1036367433735856</v>
+        <v>-0.3716575529733423</v>
       </c>
       <c r="E38">
-        <v>-0.02425375525263773</v>
+        <v>0.1285248156615645</v>
       </c>
       <c r="F38">
-        <v>0.782513731512502</v>
+        <v>0.1419164566432106</v>
       </c>
       <c r="G38">
-        <v>0.009170900044935501</v>
+        <v>0.005705970652452188</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>-0.2286872484240907</v>
+        <v>0.7328696741854634</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,25 +1655,25 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>-0.002171598322663004</v>
+        <v>0.009043940524454784</v>
       </c>
       <c r="D39">
-        <v>-0.1676592997645631</v>
+        <v>-0.6536659831396671</v>
       </c>
       <c r="E39">
-        <v>-0.02287018666719404</v>
+        <v>0.16699134482124</v>
       </c>
       <c r="F39">
-        <v>0.794637512402627</v>
+        <v>0.0556460725629605</v>
       </c>
       <c r="G39">
-        <v>0.008325771824072325</v>
+        <v>0.004683285499059118</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>-0.4521386800334167</v>
+        <v>0.5310902255639095</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1684,25 +1684,25 @@
         <v>47</v>
       </c>
       <c r="C40">
-        <v>-0.00105110973130258</v>
+        <v>0.01011430380253201</v>
       </c>
       <c r="D40">
-        <v>0.0694790005316321</v>
+        <v>-0.4143555859345331</v>
       </c>
       <c r="E40">
-        <v>-0.01093319392643337</v>
+        <v>0.186022360264134</v>
       </c>
       <c r="F40">
-        <v>0.900981299611776</v>
+        <v>0.03271337856386822</v>
       </c>
       <c r="G40">
-        <v>0.00843147139780326</v>
+        <v>0.00468545578178493</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>-0.06821637426900583</v>
+        <v>0.9106182121971595</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1713,25 +1713,25 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.0001342791399038933</v>
+        <v>0.01130140149123677</v>
       </c>
       <c r="D41">
-        <v>-0.2469518493202707</v>
+        <v>-0.7308604845446951</v>
       </c>
       <c r="E41">
-        <v>0.0014645010602182</v>
+        <v>0.2406658290637342</v>
       </c>
       <c r="F41">
-        <v>0.9867032230441799</v>
+        <v>0.005440589349624167</v>
       </c>
       <c r="G41">
-        <v>0.008041678724747094</v>
+        <v>0.003997514786323884</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>-0.2293612819928607</v>
+        <v>0.7496231108073215</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1742,25 +1742,25 @@
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.0004385617061390447</v>
+        <v>0.01193833386380594</v>
       </c>
       <c r="D42">
-        <v>0.1131176425913269</v>
+        <v>-0.3852058175742387</v>
       </c>
       <c r="E42">
-        <v>0.004762631325125302</v>
+        <v>0.2251067314853282</v>
       </c>
       <c r="F42">
-        <v>0.9567771485907296</v>
+        <v>0.009456981377712514</v>
       </c>
       <c r="G42">
-        <v>0.008076201424654312</v>
+        <v>0.004532016360218826</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.1705692260955418</v>
+        <v>1.17871591858434</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1771,25 +1771,25 @@
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.0005090276002288876</v>
+        <v>0.01197006656126784</v>
       </c>
       <c r="D43">
-        <v>-0.06440191387559815</v>
+        <v>-0.5610469355206196</v>
       </c>
       <c r="E43">
-        <v>0.005695267579983086</v>
+        <v>0.2494813153067311</v>
       </c>
       <c r="F43">
-        <v>0.9483238370335378</v>
+        <v>0.003916365607596702</v>
       </c>
       <c r="G43">
-        <v>0.007838780039945155</v>
+        <v>0.004075045869393174</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.002280701754386133</v>
+        <v>1.007031784005468</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1800,83 +1800,83 @@
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.001085312170085171</v>
+        <v>0.01231964800968417</v>
       </c>
       <c r="D44">
-        <v>-0.1870475431001746</v>
+        <v>-0.6738687628161311</v>
       </c>
       <c r="E44">
-        <v>0.01117408960770358</v>
+        <v>0.2137744258831011</v>
       </c>
       <c r="F44">
-        <v>0.8988110525306678</v>
+        <v>0.01384566820492142</v>
       </c>
       <c r="G44">
-        <v>0.008518119575519264</v>
+        <v>0.004937572086270849</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>-0.04487164881901717</v>
+        <v>0.9400051264524949</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.003068992745569683</v>
+        <v>0.01443024633060792</v>
       </c>
       <c r="D45">
-        <v>-0.3994281157439051</v>
+        <v>-0.8119993164730008</v>
       </c>
       <c r="E45">
-        <v>0.03533415160762548</v>
+        <v>0.2643102766587599</v>
       </c>
       <c r="F45">
-        <v>0.6875199289598901</v>
+        <v>0.002195224707471639</v>
       </c>
       <c r="G45">
-        <v>0.00761304223899975</v>
+        <v>0.004618087933377438</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>0.00260993392572334</v>
+        <v>1.078362952836637</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.003142937148561898</v>
+        <v>0.01472882414224319</v>
       </c>
       <c r="D46">
-        <v>-0.3228825852510063</v>
+        <v>-0.904687476266424</v>
       </c>
       <c r="E46">
-        <v>0.03315073368575434</v>
+        <v>0.3047635839530239</v>
       </c>
       <c r="F46">
-        <v>0.7059104565168808</v>
+        <v>0.0003807564423005651</v>
       </c>
       <c r="G46">
-        <v>0.008310594758107295</v>
+        <v>0.004037062733381239</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>0.08884218121060233</v>
+        <v>1.024788486367434</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1887,83 +1887,83 @@
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.003751076163691671</v>
+        <v>0.01518420443892521</v>
       </c>
       <c r="D47">
-        <v>-0.02269043821675387</v>
+        <v>-0.5181259968102074</v>
       </c>
       <c r="E47">
-        <v>0.03769350938171841</v>
+        <v>0.2379800706608441</v>
       </c>
       <c r="F47">
-        <v>0.6678511613257861</v>
+        <v>0.006000203913277219</v>
       </c>
       <c r="G47">
-        <v>0.008721855564595826</v>
+        <v>0.005435253053238776</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.4687005392268551</v>
+        <v>1.471004784688996</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.005211789014521032</v>
+        <v>0.01679348005683884</v>
       </c>
       <c r="D48">
-        <v>-0.4692762208551681</v>
+        <v>-1.119733044733045</v>
       </c>
       <c r="E48">
-        <v>0.0573049910593025</v>
+        <v>0.3378683913031774</v>
       </c>
       <c r="F48">
-        <v>0.5139762563325767</v>
+        <v>7.430831122815912E-05</v>
       </c>
       <c r="G48">
-        <v>0.00796358180938401</v>
+        <v>0.004102988687843089</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>0.2134681400470871</v>
+        <v>1.080212842712843</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.005483956247315029</v>
+        <v>0.01680611574042671</v>
       </c>
       <c r="D49">
-        <v>-0.6296536796536798</v>
+        <v>-0.9716970456444143</v>
       </c>
       <c r="E49">
-        <v>0.05990242433949355</v>
+        <v>0.3121810634901964</v>
       </c>
       <c r="F49">
-        <v>0.4950532852728974</v>
+        <v>0.0002683480009513002</v>
       </c>
       <c r="G49">
-        <v>0.008014885360552402</v>
+        <v>0.004485626051330254</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.08874458874458901</v>
+        <v>1.229904116351485</v>
       </c>
     </row>
   </sheetData>
